--- a/Exam/gymtrackerpro/lib/controller/__tests__/it/workout-session-controller/updateWorkoutSession-it-form.xlsx
+++ b/Exam/gymtrackerpro/lib/controller/__tests__/it/workout-session-controller/updateWorkoutSession-it-form.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="62">
   <si>
     <t>Statement: updateWorkoutSession(workoutSessionId: string, data: UpdateWorkoutSessionInput): Promise&lt;ActionResult&lt;WorkoutSession&gt;&gt; — validates input with Zod, delegates to workoutSessionService.updateWorkoutSession(), and returns the updated session metadata wrapped in ActionResult.</t>
   </si>
@@ -83,16 +83,17 @@
   </si>
   <si>
     <t xml:space="preserve">Member seeded via userService.createMember(). Exercise seeded via exerciseService.createExercise(). Session seeded via workoutSessionService.createWorkoutSession(): date = "2024-06-01", duration = 60, notes = "Original".
-const data: UpdateWorkoutSessionInput = { date: "2025-01-15", duration: 90, notes: "Updated" }</t>
-  </si>
-  <si>
-    <t>updateWorkoutSession(seededSession.id, data)</t>
-  </si>
-  <si>
-    <t>{ success: true, data: { date: 2025-01-15, duration: 90, notes: "Updated" } }</t>
-  </si>
-  <si>
-    <t>workout_sessions row date, duration, and notes updated</t>
+const inputId: string = seededSession.id
+const inputData: UpdateWorkoutSessionInput = { date: "2025-01-15", duration: 90, notes: "Updated" }</t>
+  </si>
+  <si>
+    <t>updateWorkoutSession(inputId, inputData)</t>
+  </si>
+  <si>
+    <t>{ success: true, data: { id: seededSession.id, date: 2025-01-15, duration: 90, notes: "Updated" } }</t>
+  </si>
+  <si>
+    <t>workout_sessions row: date, duration, and notes updated</t>
   </si>
   <si>
     <t>Passed</t>
@@ -101,56 +102,68 @@
     <t>2</t>
   </si>
   <si>
-    <t xml:space="preserve">Member seeded via userService.createMember(). Exercise seeded via exerciseService.createExercise(). Session seeded via workoutSessionService.createWorkoutSession().
-const data: UpdateWorkoutSessionInput = { duration: 90 }</t>
+    <t xml:space="preserve">Member seeded via userService.createMember(). Exercise seeded via exerciseService.createExercise(). Session seeded via workoutSessionService.createWorkoutSession(): date = "2024-06-01", duration = 60, notes = "Original".
+const inputId: string = seededSession.id
+const inputData: UpdateWorkoutSessionInput = { duration: 90 }</t>
+  </si>
+  <si>
+    <t>{ success: true, data: { duration: 90, notes: "Original" } }</t>
+  </si>
+  <si>
+    <t>duration updated; date and notes unchanged</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Member seeded via userService.createMember(). Exercise seeded via exerciseService.createExercise(). Session seeded via workoutSessionService.createWorkoutSession(): date = "2024-06-01", duration = 60, notes = "Original".
+const inputId: string = seededSession.id
+const inputData: UpdateWorkoutSessionInput = {}</t>
+  </si>
+  <si>
+    <t>{ success: true, data: { date: 2024-06-01, duration: 60, notes: "Original" } }</t>
+  </si>
+  <si>
+    <t>All fields in workout_sessions row unchanged</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empty database.
+const inputId: string = "00000000-0000-0000-0000-000000000000"
+const inputData = { date: "not-a-date" } as unknown as UpdateWorkoutSessionInput</t>
+  </si>
+  <si>
+    <t>{ success: false, message: "Validation failed", errors: { date: defined } }</t>
+  </si>
+  <si>
+    <t>No change</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empty database.
+const inputId: string = "00000000-0000-0000-0000-000000000000"
+const inputData: UpdateWorkoutSessionInput = { duration: 90 }</t>
+  </si>
+  <si>
+    <t>{ success: false, message: defined non-empty string (NotFoundError message) }</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Member seeded via userService.createMember(). Exercise seeded via exerciseService.createExercise(). Two sessions seeded: sessionA (date = "2024-01-01", duration = 60), sessionB (date = "2024-02-01", duration = 45). Prior call to updateWorkoutSession() with id "00000000-0000-0000-0000-000000000000" executed and returned { success: false }.
+const inputId: string = sessionB.id
+const inputData: UpdateWorkoutSessionInput = { duration: 90 }</t>
   </si>
   <si>
     <t>{ success: true, data: { duration: 90 } }</t>
   </si>
   <si>
-    <t>duration updated; date and notes unchanged</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Empty database.
-const data: UpdateWorkoutSessionInput = { duration: 90 }</t>
-  </si>
-  <si>
-    <t>updateWorkoutSession("00000000-0000-0000-0000-000000000000", data)</t>
-  </si>
-  <si>
-    <t>{ success: false, message: defined non-empty string (NotFoundError message) }</t>
-  </si>
-  <si>
-    <t>No change</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Member seeded via userService.createMember(). Exercise seeded via exerciseService.createExercise(). Session seeded via workoutSessionService.createWorkoutSession(): date = "2024-06-01", duration = 60, notes = "Original".
-const data: UpdateWorkoutSessionInput = {}</t>
-  </si>
-  <si>
-    <t>{ success: true, data: all fields identical to seeded row }</t>
-  </si>
-  <si>
-    <t>All fields in workout_sessions row unchanged</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Empty database.
-const input = { date: "not-a-date" } as unknown as UpdateWorkoutSessionInput</t>
-  </si>
-  <si>
-    <t>updateWorkoutSession("00000000-0000-0000-0000-000000000000", input)</t>
-  </si>
-  <si>
-    <t>{ success: false, message: "Validation failed", errors: { date: defined } }</t>
+    <t>sessionB duration updated to 90; sessionA duration unchanged at 60</t>
   </si>
   <si>
     <t>Testing</t>
@@ -835,14 +848,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="80" customWidth="1"/>
-    <col min="4" max="4" width="71" customWidth="1"/>
+    <col min="4" max="4" width="44" customWidth="1"/>
     <col min="5" max="5" width="80" customWidth="1"/>
-    <col min="6" max="6" width="58" customWidth="1"/>
+    <col min="6" max="6" width="70" customWidth="1"/>
     <col min="7" max="7" width="17" customWidth="1"/>
   </cols>
   <sheetData>
@@ -869,7 +882,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" ht="80" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" ht="95" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -892,7 +905,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" ht="65" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" ht="80" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -915,7 +928,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" ht="35" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" ht="80" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -926,61 +939,84 @@
         <v>32</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" ht="65" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" ht="50" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="6" ht="35" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" ht="50" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="F6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" ht="110" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="C7" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G6" s="6" t="s">
+      <c r="D7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7" s="6" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1009,17 +1045,17 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
@@ -1031,40 +1067,40 @@
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E5" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="J5" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="K5" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="L5" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="M5" s="4" t="s">
         <v>53</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -1072,40 +1108,40 @@
         <v>1</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C6" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E6" s="1">
         <v>0</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J6" s="1">
         <v>0</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
